--- a/2022 data/excel_outputs/369_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/369_boothwise_data.xlsx
@@ -14,11 +14,80 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="494">
   <si>
     <t>AC 369 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -211,7 +280,7 @@
     <t>P S JAMUHAR EAST SIDE</t>
   </si>
   <si>
-    <t>P S JAMUHAR WEST SIDE ????0 ??0 ????</t>
+    <t>PRA0 PA0 DAGARIYAV</t>
   </si>
   <si>
     <t>P S JAMUHAR MIDDLE SIDE</t>
@@ -1433,8 +1502,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1450,7 +1527,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1458,12 +1535,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1762,82 +1857,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="D2" t="s">
-        <v>451</v>
+        <v>474</v>
       </c>
       <c r="E2" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="F2" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="G2" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="H2" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="I2" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="J2" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="K2" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="L2" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="M2" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="N2" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="O2" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="P2" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="Q2" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="R2" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="S2" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="T2" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="U2" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="V2" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="W2" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="X2" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1845,7 +2009,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>625</v>
@@ -1919,7 +2083,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>623</v>
@@ -1993,7 +2157,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>897</v>
@@ -2067,7 +2231,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>870</v>
@@ -2141,7 +2305,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>528</v>
@@ -2215,7 +2379,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>812</v>
@@ -2289,7 +2453,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>608</v>
@@ -2363,7 +2527,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>660</v>
@@ -2437,7 +2601,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>1076</v>
@@ -2511,7 +2675,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>1075</v>
@@ -2585,7 +2749,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>1021</v>
@@ -2659,7 +2823,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>735</v>
@@ -2733,7 +2897,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>785</v>
@@ -2807,7 +2971,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>846</v>
@@ -2881,7 +3045,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>1055</v>
@@ -2955,7 +3119,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C18">
         <v>953</v>
@@ -3029,7 +3193,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>1127</v>
@@ -3103,7 +3267,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>865</v>
@@ -3177,7 +3341,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C21">
         <v>865</v>
@@ -3251,7 +3415,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <v>895</v>
@@ -3325,7 +3489,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>744</v>
@@ -3399,7 +3563,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>1119</v>
@@ -3473,7 +3637,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>997</v>
@@ -3547,7 +3711,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C26">
         <v>1143</v>
@@ -3621,7 +3785,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>1249</v>
@@ -3695,7 +3859,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>1245</v>
@@ -3769,7 +3933,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>1190</v>
@@ -3843,7 +4007,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>834</v>
@@ -3917,7 +4081,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>843</v>
@@ -3991,7 +4155,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>1223</v>
@@ -4065,7 +4229,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>1133</v>
@@ -4139,7 +4303,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>1149</v>
@@ -4213,7 +4377,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>1035</v>
@@ -4287,7 +4451,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>880</v>
@@ -4361,7 +4525,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>888</v>
@@ -4435,7 +4599,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>1092</v>
@@ -4509,7 +4673,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>1070</v>
@@ -4583,7 +4747,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>1108</v>
@@ -4657,7 +4821,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>1111</v>
@@ -4731,7 +4895,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>1040</v>
@@ -4805,7 +4969,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>894</v>
@@ -4879,7 +5043,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>757</v>
@@ -4953,7 +5117,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>1154</v>
@@ -5027,7 +5191,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>1093</v>
@@ -5101,7 +5265,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>1059</v>
@@ -5175,7 +5339,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>1032</v>
@@ -5249,7 +5413,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>1038</v>
@@ -5323,7 +5487,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>877</v>
@@ -5397,7 +5561,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>867</v>
@@ -5471,7 +5635,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>950</v>
@@ -5545,7 +5709,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>826</v>
@@ -5619,7 +5783,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>1011</v>
@@ -5693,7 +5857,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>677</v>
@@ -5767,7 +5931,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>690</v>
@@ -5841,7 +6005,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>1146</v>
@@ -5915,7 +6079,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>1015</v>
@@ -5989,7 +6153,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>961</v>
@@ -6063,7 +6227,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>900</v>
@@ -6137,7 +6301,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>524</v>
@@ -6211,7 +6375,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>846</v>
@@ -6285,7 +6449,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>821</v>
@@ -6359,7 +6523,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C64">
         <v>918</v>
@@ -6433,7 +6597,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>915</v>
@@ -6507,7 +6671,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>841</v>
@@ -6581,7 +6745,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>948</v>
@@ -6655,7 +6819,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>813</v>
@@ -6729,7 +6893,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>897</v>
@@ -6803,7 +6967,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>597</v>
@@ -6877,7 +7041,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>750</v>
@@ -6951,7 +7115,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>1053</v>
@@ -7025,7 +7189,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>1057</v>
@@ -7099,7 +7263,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>1082</v>
@@ -7173,7 +7337,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>1163</v>
@@ -7247,7 +7411,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>1026</v>
@@ -7321,7 +7485,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>717</v>
@@ -7395,7 +7559,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>682</v>
@@ -7469,7 +7633,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>698</v>
@@ -7543,7 +7707,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>620</v>
@@ -7617,7 +7781,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>623</v>
@@ -7691,7 +7855,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>813</v>
@@ -7765,7 +7929,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="C83">
         <v>952</v>
@@ -7839,7 +8003,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>899</v>
@@ -7913,7 +8077,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>1217</v>
@@ -7987,7 +8151,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>1235</v>
@@ -8061,7 +8225,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C87">
         <v>1230</v>
@@ -8135,7 +8299,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C88">
         <v>887</v>
@@ -8209,7 +8373,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C89">
         <v>492</v>
@@ -8283,7 +8447,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>892</v>
@@ -8357,7 +8521,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>903</v>
@@ -8431,7 +8595,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C92">
         <v>821</v>
@@ -8505,7 +8669,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>935</v>
@@ -8579,7 +8743,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C94">
         <v>888</v>
@@ -8653,7 +8817,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C95">
         <v>672</v>
@@ -8727,7 +8891,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C96">
         <v>662</v>
@@ -8801,7 +8965,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C97">
         <v>988</v>
@@ -8875,7 +9039,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C98">
         <v>741</v>
@@ -8949,7 +9113,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C99">
         <v>952</v>
@@ -9023,7 +9187,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>802</v>
@@ -9097,7 +9261,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C101">
         <v>827</v>
@@ -9171,7 +9335,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="C102">
         <v>802</v>
@@ -9245,7 +9409,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C103">
         <v>656</v>
@@ -9319,7 +9483,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C104">
         <v>686</v>
@@ -9393,7 +9557,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C105">
         <v>653</v>
@@ -9467,7 +9631,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C106">
         <v>698</v>
@@ -9541,7 +9705,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C107">
         <v>930</v>
@@ -9615,7 +9779,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C108">
         <v>697</v>
@@ -9689,7 +9853,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="C109">
         <v>848</v>
@@ -9763,7 +9927,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C110">
         <v>883</v>
@@ -9837,7 +10001,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C111">
         <v>662</v>
@@ -9911,7 +10075,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C112">
         <v>623</v>
@@ -9985,7 +10149,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>808</v>
@@ -10059,7 +10223,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="C114">
         <v>747</v>
@@ -10133,7 +10297,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C115">
         <v>872</v>
@@ -10207,7 +10371,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="C116">
         <v>986</v>
@@ -10281,7 +10445,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C117">
         <v>1002</v>
@@ -10355,7 +10519,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C118">
         <v>986</v>
@@ -10429,7 +10593,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>1179</v>
@@ -10503,7 +10667,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>582</v>
@@ -10577,7 +10741,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>697</v>
@@ -10651,7 +10815,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>1161</v>
@@ -10725,7 +10889,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>964</v>
@@ -10799,7 +10963,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>1051</v>
@@ -10873,7 +11037,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C125">
         <v>710</v>
@@ -10947,7 +11111,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C126">
         <v>1251</v>
@@ -11021,7 +11185,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C127">
         <v>1036</v>
@@ -11095,7 +11259,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>1032</v>
@@ -11169,7 +11333,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C129">
         <v>892</v>
@@ -11243,7 +11407,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C130">
         <v>1123</v>
@@ -11317,7 +11481,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="C131">
         <v>1233</v>
@@ -11391,7 +11555,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C132">
         <v>723</v>
@@ -11465,7 +11629,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>706</v>
@@ -11539,7 +11703,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>867</v>
@@ -11613,7 +11777,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C135">
         <v>866</v>
@@ -11687,7 +11851,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C136">
         <v>1155</v>
@@ -11761,7 +11925,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>1142</v>
@@ -11835,7 +11999,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>977</v>
@@ -11909,7 +12073,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>950</v>
@@ -11983,7 +12147,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C140">
         <v>1002</v>
@@ -12057,7 +12221,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="C141">
         <v>848</v>
@@ -12131,7 +12295,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C142">
         <v>856</v>
@@ -12205,7 +12369,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C143">
         <v>964</v>
@@ -12279,7 +12443,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="C144">
         <v>908</v>
@@ -12353,7 +12517,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C145">
         <v>1114</v>
@@ -12427,7 +12591,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C146">
         <v>1196</v>
@@ -12501,7 +12665,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>693</v>
@@ -12575,7 +12739,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C148">
         <v>496</v>
@@ -12649,7 +12813,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C149">
         <v>961</v>
@@ -12723,7 +12887,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>1053</v>
@@ -12797,7 +12961,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="C151">
         <v>917</v>
@@ -12871,7 +13035,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>863</v>
@@ -12945,7 +13109,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C153">
         <v>889</v>
@@ -13019,7 +13183,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>1145</v>
@@ -13093,7 +13257,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C155">
         <v>1244</v>
@@ -13167,7 +13331,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>1142</v>
@@ -13241,7 +13405,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C157">
         <v>1061</v>
@@ -13315,7 +13479,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C158">
         <v>1097</v>
@@ -13389,7 +13553,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C159">
         <v>1096</v>
@@ -13463,7 +13627,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C160">
         <v>956</v>
@@ -13537,7 +13701,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C161">
         <v>913</v>
@@ -13611,7 +13775,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C162">
         <v>856</v>
@@ -13685,7 +13849,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>942</v>
@@ -13759,7 +13923,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C164">
         <v>970</v>
@@ -13833,7 +13997,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="C165">
         <v>952</v>
@@ -13907,7 +14071,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C166">
         <v>1020</v>
@@ -13981,7 +14145,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="C167">
         <v>1070</v>
@@ -14055,7 +14219,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C168">
         <v>1052</v>
@@ -14129,7 +14293,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C169">
         <v>727</v>
@@ -14203,7 +14367,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C170">
         <v>767</v>
@@ -14277,7 +14441,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C171">
         <v>765</v>
@@ -14351,7 +14515,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C172">
         <v>1014</v>
@@ -14425,7 +14589,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C173">
         <v>810</v>
@@ -14499,7 +14663,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="C174">
         <v>862</v>
@@ -14573,7 +14737,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C175">
         <v>926</v>
@@ -14647,7 +14811,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="C176">
         <v>827</v>
@@ -14721,7 +14885,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>948</v>
@@ -14795,7 +14959,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>1100</v>
@@ -14869,7 +15033,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>1103</v>
@@ -14943,7 +15107,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>1207</v>
@@ -15017,7 +15181,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>1012</v>
@@ -15091,7 +15255,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>983</v>
@@ -15165,7 +15329,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>1172</v>
@@ -15239,7 +15403,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>1141</v>
@@ -15313,7 +15477,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>935</v>
@@ -15387,7 +15551,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>1133</v>
@@ -15461,7 +15625,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>909</v>
@@ -15535,7 +15699,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>1184</v>
@@ -15609,7 +15773,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>817</v>
@@ -15683,7 +15847,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>1194</v>
@@ -15757,7 +15921,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>1043</v>
@@ -15831,7 +15995,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>839</v>
@@ -15905,7 +16069,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>905</v>
@@ -15979,7 +16143,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="C194">
         <v>784</v>
@@ -16053,7 +16217,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="C195">
         <v>830</v>
@@ -16127,7 +16291,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="C196">
         <v>787</v>
@@ -16201,7 +16365,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C197">
         <v>933</v>
@@ -16275,7 +16439,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C198">
         <v>963</v>
@@ -16349,7 +16513,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C199">
         <v>981</v>
@@ -16423,7 +16587,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C200">
         <v>939</v>
@@ -16497,7 +16661,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="C201">
         <v>1080</v>
@@ -16571,7 +16735,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C202">
         <v>985</v>
@@ -16645,7 +16809,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C203">
         <v>1217</v>
@@ -16719,7 +16883,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C204">
         <v>1187</v>
@@ -16793,7 +16957,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C205">
         <v>1175</v>
@@ -16867,7 +17031,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>1059</v>
@@ -16941,7 +17105,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="C207">
         <v>853</v>
@@ -17015,7 +17179,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="C208">
         <v>834</v>
@@ -17089,7 +17253,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C209">
         <v>873</v>
@@ -17163,7 +17327,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="C210">
         <v>927</v>
@@ -17237,7 +17401,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C211">
         <v>997</v>
@@ -17311,7 +17475,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="C212">
         <v>904</v>
@@ -17385,7 +17549,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C213">
         <v>848</v>
@@ -17459,7 +17623,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="C214">
         <v>967</v>
@@ -17533,7 +17697,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="C215">
         <v>1051</v>
@@ -17607,7 +17771,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="C216">
         <v>700</v>
@@ -17681,7 +17845,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C217">
         <v>705</v>
@@ -17755,7 +17919,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>760</v>
@@ -17829,7 +17993,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="C219">
         <v>690</v>
@@ -17903,7 +18067,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C220">
         <v>601</v>
@@ -17977,7 +18141,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C221">
         <v>690</v>
@@ -18051,7 +18215,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C222">
         <v>1047</v>
@@ -18125,7 +18289,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="C223">
         <v>1071</v>
@@ -18199,7 +18363,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C224">
         <v>1010</v>
@@ -18273,7 +18437,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="C225">
         <v>860</v>
@@ -18347,7 +18511,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C226">
         <v>688</v>
@@ -18421,7 +18585,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="C227">
         <v>830</v>
@@ -18495,7 +18659,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="C228">
         <v>940</v>
@@ -18569,7 +18733,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C229">
         <v>715</v>
@@ -18643,7 +18807,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="C230">
         <v>739</v>
@@ -18717,7 +18881,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C231">
         <v>336</v>
@@ -18791,7 +18955,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C232">
         <v>688</v>
@@ -18865,7 +19029,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C233">
         <v>839</v>
@@ -18939,7 +19103,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="C234">
         <v>882</v>
@@ -19013,7 +19177,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C235">
         <v>538</v>
@@ -19087,7 +19251,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="C236">
         <v>668</v>
@@ -19161,7 +19325,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="C237">
         <v>636</v>
@@ -19235,7 +19399,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="C238">
         <v>1096</v>
@@ -19309,7 +19473,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C239">
         <v>856</v>
@@ -19383,7 +19547,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="C240">
         <v>834</v>
@@ -19457,7 +19621,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="C241">
         <v>869</v>
@@ -19531,7 +19695,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="C242">
         <v>828</v>
@@ -19605,7 +19769,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C243">
         <v>953</v>
@@ -19679,7 +19843,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="C244">
         <v>805</v>
@@ -19753,7 +19917,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C245">
         <v>678</v>
@@ -19827,7 +19991,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="C246">
         <v>483</v>
@@ -19901,7 +20065,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="C247">
         <v>909</v>
@@ -19975,7 +20139,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="C248">
         <v>722</v>
@@ -20049,7 +20213,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="C249">
         <v>320</v>
@@ -20123,7 +20287,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="C250">
         <v>674</v>
@@ -20197,7 +20361,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C251">
         <v>1163</v>
@@ -20271,7 +20435,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="C252">
         <v>887</v>
@@ -20345,7 +20509,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="C253">
         <v>621</v>
@@ -20419,7 +20583,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="C254">
         <v>607</v>
@@ -20493,7 +20657,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="C255">
         <v>636</v>
@@ -20567,7 +20731,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="C256">
         <v>893</v>
@@ -20641,7 +20805,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="C257">
         <v>874</v>
@@ -20715,7 +20879,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="C258">
         <v>932</v>
@@ -20789,7 +20953,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="C259">
         <v>570</v>
@@ -20863,7 +21027,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="C260">
         <v>957</v>
@@ -20937,7 +21101,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C261">
         <v>719</v>
@@ -21011,7 +21175,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="C262">
         <v>876</v>
@@ -21085,7 +21249,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="C263">
         <v>858</v>
@@ -21159,7 +21323,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="C264">
         <v>997</v>
@@ -21233,7 +21397,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="C265">
         <v>1137</v>
@@ -21307,7 +21471,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="C266">
         <v>705</v>
@@ -21381,7 +21545,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="C267">
         <v>707</v>
@@ -21455,7 +21619,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C268">
         <v>679</v>
@@ -21529,7 +21693,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="C269">
         <v>699</v>
@@ -21603,7 +21767,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="C270">
         <v>1202</v>
@@ -21677,7 +21841,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="C271">
         <v>1167</v>
@@ -21751,7 +21915,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="C272">
         <v>1182</v>
@@ -21825,7 +21989,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C273">
         <v>1177</v>
@@ -21899,7 +22063,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="C274">
         <v>991</v>
@@ -21973,7 +22137,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="C275">
         <v>1003</v>
@@ -22047,7 +22211,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="C276">
         <v>450</v>
@@ -22121,7 +22285,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="C277">
         <v>1112</v>
@@ -22195,7 +22359,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="C278">
         <v>1072</v>
@@ -22269,7 +22433,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="C279">
         <v>714</v>
@@ -22343,7 +22507,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="C280">
         <v>820</v>
@@ -22417,7 +22581,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="C281">
         <v>893</v>
@@ -22491,7 +22655,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="C282">
         <v>868</v>
@@ -22565,7 +22729,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="C283">
         <v>1210</v>
@@ -22639,7 +22803,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="C284">
         <v>1106</v>
@@ -22713,7 +22877,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="C285">
         <v>660</v>
@@ -22787,7 +22951,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="C286">
         <v>1110</v>
@@ -22861,7 +23025,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="C287">
         <v>1172</v>
@@ -22935,7 +23099,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="C288">
         <v>655</v>
@@ -23009,7 +23173,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="C289">
         <v>684</v>
@@ -23083,7 +23247,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="C290">
         <v>840</v>
@@ -23157,7 +23321,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="C291">
         <v>808</v>
@@ -23231,7 +23395,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="C292">
         <v>733</v>
@@ -23305,7 +23469,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="C293">
         <v>608</v>
@@ -23379,7 +23543,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="C294">
         <v>710</v>
@@ -23453,7 +23617,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="C295">
         <v>838</v>
@@ -23527,7 +23691,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="C296">
         <v>794</v>
@@ -23601,7 +23765,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="C297">
         <v>828</v>
@@ -23675,7 +23839,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C298">
         <v>1080</v>
@@ -23749,7 +23913,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="C299">
         <v>832</v>
@@ -23823,7 +23987,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="C300">
         <v>1029</v>
@@ -23897,7 +24061,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C301">
         <v>968</v>
@@ -23971,7 +24135,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="C302">
         <v>414</v>
@@ -24045,7 +24209,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="C303">
         <v>634</v>
@@ -24119,7 +24283,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="C304">
         <v>918</v>
@@ -24193,7 +24357,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="C305">
         <v>360</v>
@@ -24267,7 +24431,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="C306">
         <v>736</v>
@@ -24341,7 +24505,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="C307">
         <v>637</v>
@@ -24415,7 +24579,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C308">
         <v>716</v>
@@ -24489,7 +24653,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="C309">
         <v>1028</v>
@@ -24563,7 +24727,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C310">
         <v>1048</v>
@@ -24637,7 +24801,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C311">
         <v>641</v>
@@ -24711,7 +24875,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="C312">
         <v>704</v>
@@ -24785,7 +24949,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="C313">
         <v>664</v>
@@ -24859,7 +25023,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C314">
         <v>711</v>
@@ -24933,7 +25097,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="C315">
         <v>641</v>
@@ -25007,7 +25171,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="C316">
         <v>708</v>
@@ -25081,7 +25245,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C317">
         <v>981</v>
@@ -25155,7 +25319,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C318">
         <v>986</v>
@@ -25229,7 +25393,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C319">
         <v>1173</v>
@@ -25303,7 +25467,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="C320">
         <v>819</v>
@@ -25377,7 +25541,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C321">
         <v>657</v>
@@ -25451,7 +25615,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C322">
         <v>687</v>
@@ -25525,7 +25689,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="C323">
         <v>621</v>
@@ -25599,7 +25763,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="C324">
         <v>679</v>
@@ -25673,7 +25837,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="C325">
         <v>1014</v>
@@ -25747,7 +25911,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="C326">
         <v>887</v>
@@ -25821,7 +25985,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="C327">
         <v>1163</v>
@@ -25895,7 +26059,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="C328">
         <v>1119</v>
@@ -25969,7 +26133,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="C329">
         <v>1138</v>
@@ -26043,7 +26207,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="C330">
         <v>1054</v>
@@ -26117,7 +26281,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="C331">
         <v>1106</v>
@@ -26191,7 +26355,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="C332">
         <v>1045</v>
@@ -26265,7 +26429,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="C333">
         <v>583</v>
@@ -26339,7 +26503,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="C334">
         <v>1011</v>
@@ -26413,7 +26577,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="C335">
         <v>840</v>
@@ -26487,7 +26651,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="C336">
         <v>755</v>
@@ -26561,7 +26725,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="C337">
         <v>425</v>
@@ -26635,7 +26799,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="C338">
         <v>1017</v>
@@ -26709,7 +26873,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="C339">
         <v>1120</v>
@@ -26783,7 +26947,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="C340">
         <v>1090</v>
@@ -26857,7 +27021,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C341">
         <v>1240</v>
@@ -26931,7 +27095,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="C342">
         <v>1096</v>
@@ -27005,7 +27169,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="C343">
         <v>621</v>
@@ -27079,7 +27243,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="C344">
         <v>973</v>
@@ -27153,7 +27317,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="C345">
         <v>896</v>
@@ -27227,7 +27391,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="C346">
         <v>896</v>
@@ -27301,7 +27465,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C347">
         <v>925</v>
@@ -27375,7 +27539,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="C348">
         <v>806</v>
@@ -27449,7 +27613,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="C349">
         <v>774</v>
@@ -27523,7 +27687,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="C350">
         <v>709</v>
@@ -27597,7 +27761,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="C351">
         <v>945</v>
@@ -27671,7 +27835,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="C352">
         <v>648</v>
@@ -27745,7 +27909,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="C353">
         <v>1105</v>
@@ -27819,7 +27983,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="C354">
         <v>820</v>
@@ -27893,7 +28057,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="C355">
         <v>818</v>
@@ -27967,7 +28131,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="C356">
         <v>775</v>
@@ -28041,7 +28205,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="C357">
         <v>1225</v>
@@ -28115,7 +28279,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="C358">
         <v>1208</v>
@@ -28189,7 +28353,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C359">
         <v>1038</v>
@@ -28263,7 +28427,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="C360">
         <v>656</v>
@@ -28337,7 +28501,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="C361">
         <v>653</v>
@@ -28411,7 +28575,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="C362">
         <v>1062</v>
@@ -28485,7 +28649,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="C363">
         <v>985</v>
@@ -28559,7 +28723,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="C364">
         <v>641</v>
@@ -28633,7 +28797,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="C365">
         <v>592</v>
@@ -28707,7 +28871,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="C366">
         <v>706</v>
@@ -28781,7 +28945,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="C367">
         <v>1039</v>
@@ -28855,7 +29019,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="C368">
         <v>954</v>
@@ -28929,7 +29093,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="C369">
         <v>977</v>
@@ -29003,7 +29167,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="C370">
         <v>1006</v>
@@ -29077,7 +29241,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="C371">
         <v>1083</v>
@@ -29151,7 +29315,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="C372">
         <v>1026</v>
@@ -29225,7 +29389,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="C373">
         <v>861</v>
@@ -29299,7 +29463,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="C374">
         <v>546</v>
@@ -29373,7 +29537,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="C375">
         <v>688</v>
@@ -29447,7 +29611,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="C376">
         <v>681</v>
@@ -29521,7 +29685,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="C377">
         <v>892</v>
@@ -29595,7 +29759,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="C378">
         <v>559</v>
@@ -29669,7 +29833,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="C379">
         <v>1186</v>
@@ -29743,7 +29907,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="C380">
         <v>1171</v>
@@ -29817,7 +29981,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="C381">
         <v>635</v>
@@ -29891,7 +30055,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="C382">
         <v>1083</v>
@@ -29965,7 +30129,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="C383">
         <v>826</v>
@@ -30039,7 +30203,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="C384">
         <v>912</v>
@@ -30113,7 +30277,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="C385">
         <v>717</v>
@@ -30187,7 +30351,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="C386">
         <v>951</v>
@@ -30261,7 +30425,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="C387">
         <v>1046</v>
@@ -30335,7 +30499,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="C388">
         <v>492</v>
@@ -30409,7 +30573,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="C389">
         <v>832</v>
@@ -30483,7 +30647,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="C390">
         <v>925</v>
@@ -30557,7 +30721,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="C391">
         <v>448</v>
@@ -30631,7 +30795,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="C392">
         <v>1118</v>
@@ -30705,7 +30869,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="C393">
         <v>1120</v>
@@ -30779,7 +30943,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="C394">
         <v>899</v>
@@ -30853,7 +31017,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="C395">
         <v>746</v>
@@ -30927,7 +31091,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="C396">
         <v>871</v>
@@ -31001,7 +31165,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="C397">
         <v>882</v>
@@ -31075,7 +31239,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="C398">
         <v>864</v>
@@ -31149,7 +31313,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="C399">
         <v>1026</v>
@@ -31223,7 +31387,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="C400">
         <v>1002</v>
@@ -31297,7 +31461,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="C401">
         <v>544</v>
@@ -31371,7 +31535,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="C402">
         <v>634</v>
@@ -31445,7 +31609,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="C403">
         <v>635</v>
@@ -31519,7 +31683,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="C404">
         <v>1124</v>
@@ -31593,7 +31757,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="C405">
         <v>1119</v>
@@ -31667,7 +31831,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="C406">
         <v>1089</v>
@@ -31741,7 +31905,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="C407">
         <v>793</v>
@@ -31815,7 +31979,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="C408">
         <v>798</v>
@@ -31889,7 +32053,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="C409">
         <v>850</v>
@@ -31963,7 +32127,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="C410">
         <v>814</v>
@@ -32037,7 +32201,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="C411">
         <v>895</v>
@@ -32111,7 +32275,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="C412">
         <v>719</v>
@@ -32185,7 +32349,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="C413">
         <v>689</v>
@@ -32259,7 +32423,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="C414">
         <v>639</v>
@@ -32333,7 +32497,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="C415">
         <v>634</v>
@@ -32407,7 +32571,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="C416">
         <v>985</v>
@@ -32481,7 +32645,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="C417">
         <v>930</v>
@@ -32555,7 +32719,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="C418">
         <v>906</v>
@@ -32629,7 +32793,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="C419">
         <v>1186</v>
@@ -32703,7 +32867,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="C420">
         <v>800</v>
@@ -32777,7 +32941,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="C421">
         <v>783</v>
@@ -32851,7 +33015,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="C422">
         <v>723</v>
@@ -32925,7 +33089,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="C423">
         <v>1166</v>
@@ -32999,7 +33163,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="C424">
         <v>1149</v>
@@ -33073,7 +33237,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="C425">
         <v>1212</v>
@@ -33147,7 +33311,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="C426">
         <v>662</v>
@@ -33221,7 +33385,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="C427">
         <v>646</v>
@@ -33295,7 +33459,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="C428">
         <v>1090</v>
@@ -33369,7 +33533,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="C429">
         <v>1065</v>
@@ -33443,7 +33607,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="C430">
         <v>987</v>
@@ -33517,7 +33681,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="C431">
         <v>890</v>
@@ -33591,7 +33755,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="C432">
         <v>698</v>
@@ -33665,7 +33829,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="C433">
         <v>686</v>
@@ -33739,7 +33903,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="C434">
         <v>1120</v>
@@ -33813,7 +33977,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="C435">
         <v>1009</v>
@@ -33887,7 +34051,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="C436">
         <v>782</v>
@@ -33961,7 +34125,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="C437">
         <v>727</v>
@@ -34035,7 +34199,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>434</v>
+        <v>457</v>
       </c>
       <c r="C438">
         <v>1115</v>
@@ -34109,7 +34273,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="C439">
         <v>916</v>
@@ -34183,7 +34347,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="C440">
         <v>838</v>
@@ -34257,7 +34421,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="C441">
         <v>1184</v>
@@ -34331,7 +34495,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="C442">
         <v>635</v>
@@ -34405,7 +34569,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="C443">
         <v>633</v>
@@ -34479,7 +34643,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="C444">
         <v>1112</v>
@@ -34553,7 +34717,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="C445">
         <v>961</v>
@@ -34627,7 +34791,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="C446">
         <v>976</v>
@@ -34701,7 +34865,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="C447">
         <v>1218</v>
@@ -34775,7 +34939,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="C448">
         <v>963</v>
@@ -34849,7 +35013,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="C449">
         <v>735</v>
@@ -34923,7 +35087,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="C450">
         <v>1012</v>
@@ -34997,7 +35161,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="C451">
         <v>984</v>
@@ -35071,7 +35235,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="C452">
         <v>756</v>
@@ -35145,7 +35309,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="C453">
         <v>703</v>
